--- a/Config/Excels/Local/L-Localization-通用.xlsx
+++ b/Config/Excels/Local/L-Localization-通用.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24645" windowHeight="11610" tabRatio="671"/>
+    <workbookView windowHeight="18450" tabRatio="671"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205">
   <si>
     <t>##var</t>
   </si>
@@ -25,6 +25,9 @@
     <t>key</t>
   </si>
   <si>
+    <t>is_code</t>
+  </si>
+  <si>
     <t>ChineseSimplified</t>
   </si>
   <si>
@@ -73,10 +76,16 @@
     <t>string</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t>是否导出到代码中</t>
   </si>
   <si>
     <t>简体中文</t>
@@ -628,8 +637,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
@@ -663,15 +672,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -680,6 +696,61 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -694,46 +765,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -756,30 +788,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -800,181 +809,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1006,19 +1015,47 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1040,33 +1077,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1086,17 +1101,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1108,10 +1117,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1120,144 +1129,150 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="31" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1579,743 +1594,789 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="16.125" customWidth="1"/>
     <col min="3" max="3" width="23.375" customWidth="1"/>
-    <col min="4" max="5" width="18.75" customWidth="1"/>
-    <col min="6" max="6" width="16.125" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="27" customWidth="1"/>
-    <col min="9" max="9" width="25.875" customWidth="1"/>
-    <col min="10" max="10" width="17" customWidth="1"/>
-    <col min="11" max="11" width="21.625" customWidth="1"/>
-    <col min="12" max="12" width="18.125" customWidth="1"/>
-    <col min="13" max="13" width="19.5" customWidth="1"/>
-    <col min="14" max="14" width="19.375" customWidth="1"/>
-    <col min="15" max="15" width="20.5" customWidth="1"/>
-    <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="17.75" customWidth="1"/>
+    <col min="4" max="4" width="15" style="2" customWidth="1"/>
+    <col min="5" max="6" width="18.75" customWidth="1"/>
+    <col min="7" max="7" width="16.125" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="27" customWidth="1"/>
+    <col min="10" max="10" width="25.875" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
+    <col min="12" max="12" width="21.625" customWidth="1"/>
+    <col min="13" max="13" width="18.125" customWidth="1"/>
+    <col min="14" max="14" width="19.5" customWidth="1"/>
+    <col min="15" max="15" width="19.375" customWidth="1"/>
+    <col min="16" max="16" width="20.5" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="18" max="18" width="17.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:17">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:18">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:17">
-      <c r="A2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:18">
+      <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>18</v>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:17">
-      <c r="A3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" ht="28.5" spans="1:18">
+      <c r="A3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="N3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="O3" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="P3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="4" spans="3:17">
+    <row r="4" spans="3:18">
       <c r="C4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" t="s">
-        <v>36</v>
+        <v>38</v>
+      </c>
+      <c r="D4" s="4" t="b">
+        <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" t="s">
+        <v>47</v>
+      </c>
+      <c r="N4" t="s">
+        <v>48</v>
+      </c>
+      <c r="O4" t="s">
+        <v>49</v>
+      </c>
+      <c r="P4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>51</v>
+      </c>
+      <c r="R4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="3:18">
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M5" t="s">
+        <v>62</v>
+      </c>
+      <c r="N5" t="s">
+        <v>63</v>
+      </c>
+      <c r="O5" t="s">
+        <v>64</v>
+      </c>
+      <c r="P5" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>66</v>
+      </c>
+      <c r="R5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="3:18">
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I6" t="s">
+        <v>73</v>
+      </c>
+      <c r="J6" t="s">
+        <v>74</v>
+      </c>
+      <c r="K6" t="s">
+        <v>75</v>
+      </c>
+      <c r="L6" t="s">
+        <v>76</v>
+      </c>
+      <c r="M6" t="s">
+        <v>77</v>
+      </c>
+      <c r="N6" t="s">
+        <v>78</v>
+      </c>
+      <c r="O6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P6" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>81</v>
+      </c>
+      <c r="R6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="3:18">
+      <c r="C7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I7" t="s">
+        <v>88</v>
+      </c>
+      <c r="J7" t="s">
+        <v>89</v>
+      </c>
+      <c r="K7" t="s">
+        <v>90</v>
+      </c>
+      <c r="L7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M7" t="s">
+        <v>91</v>
+      </c>
+      <c r="N7" t="s">
+        <v>92</v>
+      </c>
+      <c r="O7" t="s">
+        <v>93</v>
+      </c>
+      <c r="P7" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>95</v>
+      </c>
+      <c r="R7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="3:18">
+      <c r="C8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H8" t="s">
+        <v>101</v>
+      </c>
+      <c r="I8" t="s">
+        <v>102</v>
+      </c>
+      <c r="J8" t="s">
+        <v>103</v>
+      </c>
+      <c r="K8" t="s">
+        <v>104</v>
+      </c>
+      <c r="L8" t="s">
+        <v>105</v>
+      </c>
+      <c r="M8" t="s">
+        <v>106</v>
+      </c>
+      <c r="N8" t="s">
+        <v>107</v>
+      </c>
+      <c r="O8" t="s">
+        <v>108</v>
+      </c>
+      <c r="P8" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>110</v>
+      </c>
+      <c r="R8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="3:18">
+      <c r="C9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G9" t="s">
+        <v>115</v>
+      </c>
+      <c r="H9" t="s">
+        <v>116</v>
+      </c>
+      <c r="I9" t="s">
+        <v>117</v>
+      </c>
+      <c r="J9" t="s">
+        <v>118</v>
+      </c>
+      <c r="K9" t="s">
+        <v>119</v>
+      </c>
+      <c r="L9" t="s">
+        <v>120</v>
+      </c>
+      <c r="M9" t="s">
+        <v>121</v>
+      </c>
+      <c r="N9" t="s">
+        <v>122</v>
+      </c>
+      <c r="O9" t="s">
+        <v>123</v>
+      </c>
+      <c r="P9" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>125</v>
+      </c>
+      <c r="R9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="3:18">
+      <c r="C10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
         <v>39</v>
       </c>
-      <c r="H4" t="s">
+      <c r="F10" t="s">
         <v>40</v>
       </c>
-      <c r="I4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K4" t="s">
-        <v>43</v>
-      </c>
-      <c r="L4" t="s">
-        <v>44</v>
-      </c>
-      <c r="M4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N4" t="s">
-        <v>46</v>
-      </c>
-      <c r="O4" t="s">
-        <v>47</v>
-      </c>
-      <c r="P4" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>49</v>
+      <c r="G10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H10" t="s">
+        <v>129</v>
+      </c>
+      <c r="I10" t="s">
+        <v>130</v>
+      </c>
+      <c r="J10" t="s">
+        <v>131</v>
+      </c>
+      <c r="K10" t="s">
+        <v>132</v>
+      </c>
+      <c r="L10" t="s">
+        <v>133</v>
+      </c>
+      <c r="M10" t="s">
+        <v>134</v>
+      </c>
+      <c r="N10" t="s">
+        <v>135</v>
+      </c>
+      <c r="O10" t="s">
+        <v>136</v>
+      </c>
+      <c r="P10" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>138</v>
+      </c>
+      <c r="R10" t="s">
+        <v>139</v>
       </c>
     </row>
-    <row r="5" spans="3:17">
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" t="s">
-        <v>55</v>
-      </c>
-      <c r="I5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J5" t="s">
-        <v>57</v>
-      </c>
-      <c r="K5" t="s">
-        <v>58</v>
-      </c>
-      <c r="L5" t="s">
-        <v>59</v>
-      </c>
-      <c r="M5" t="s">
-        <v>60</v>
-      </c>
-      <c r="N5" t="s">
-        <v>61</v>
-      </c>
-      <c r="O5" t="s">
-        <v>62</v>
-      </c>
-      <c r="P5" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>64</v>
+    <row r="11" spans="3:18">
+      <c r="C11" t="s">
+        <v>140</v>
+      </c>
+      <c r="D11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>141</v>
+      </c>
+      <c r="F11" t="s">
+        <v>142</v>
+      </c>
+      <c r="G11" t="s">
+        <v>143</v>
+      </c>
+      <c r="H11" t="s">
+        <v>144</v>
+      </c>
+      <c r="I11" t="s">
+        <v>145</v>
+      </c>
+      <c r="J11" t="s">
+        <v>146</v>
+      </c>
+      <c r="K11" t="s">
+        <v>147</v>
+      </c>
+      <c r="L11" t="s">
+        <v>148</v>
+      </c>
+      <c r="M11" t="s">
+        <v>149</v>
+      </c>
+      <c r="N11" t="s">
+        <v>150</v>
+      </c>
+      <c r="O11" t="s">
+        <v>151</v>
+      </c>
+      <c r="P11" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>152</v>
+      </c>
+      <c r="R11" t="s">
+        <v>153</v>
       </c>
     </row>
-    <row r="6" spans="3:17">
-      <c r="C6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" t="s">
-        <v>69</v>
-      </c>
-      <c r="H6" t="s">
-        <v>70</v>
-      </c>
-      <c r="I6" t="s">
-        <v>71</v>
-      </c>
-      <c r="J6" t="s">
-        <v>72</v>
-      </c>
-      <c r="K6" t="s">
-        <v>73</v>
-      </c>
-      <c r="L6" t="s">
-        <v>74</v>
-      </c>
-      <c r="M6" t="s">
-        <v>75</v>
-      </c>
-      <c r="N6" t="s">
-        <v>76</v>
-      </c>
-      <c r="O6" t="s">
-        <v>77</v>
-      </c>
-      <c r="P6" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>79</v>
+    <row r="12" spans="3:18">
+      <c r="C12" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>155</v>
+      </c>
+      <c r="F12" t="s">
+        <v>156</v>
+      </c>
+      <c r="G12" t="s">
+        <v>157</v>
+      </c>
+      <c r="H12" t="s">
+        <v>158</v>
+      </c>
+      <c r="I12" t="s">
+        <v>159</v>
+      </c>
+      <c r="J12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K12" t="s">
+        <v>157</v>
+      </c>
+      <c r="L12" t="s">
+        <v>157</v>
+      </c>
+      <c r="M12" t="s">
+        <v>157</v>
+      </c>
+      <c r="N12" t="s">
+        <v>161</v>
+      </c>
+      <c r="O12" t="s">
+        <v>157</v>
+      </c>
+      <c r="P12" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>157</v>
+      </c>
+      <c r="R12" t="s">
+        <v>157</v>
       </c>
     </row>
-    <row r="7" spans="3:17">
-      <c r="C7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F7" t="s">
-        <v>83</v>
-      </c>
-      <c r="G7" t="s">
-        <v>84</v>
-      </c>
-      <c r="H7" t="s">
-        <v>85</v>
-      </c>
-      <c r="I7" t="s">
-        <v>86</v>
-      </c>
-      <c r="J7" t="s">
-        <v>87</v>
-      </c>
-      <c r="K7" t="s">
-        <v>88</v>
-      </c>
-      <c r="L7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M7" t="s">
-        <v>89</v>
-      </c>
-      <c r="N7" t="s">
-        <v>90</v>
-      </c>
-      <c r="O7" t="s">
-        <v>91</v>
-      </c>
-      <c r="P7" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>93</v>
+    <row r="13" spans="3:18">
+      <c r="C13" t="s">
+        <v>162</v>
+      </c>
+      <c r="D13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>163</v>
+      </c>
+      <c r="F13" t="s">
+        <v>163</v>
+      </c>
+      <c r="G13" t="s">
+        <v>164</v>
+      </c>
+      <c r="H13" t="s">
+        <v>165</v>
+      </c>
+      <c r="I13" t="s">
+        <v>166</v>
+      </c>
+      <c r="J13" t="s">
+        <v>167</v>
+      </c>
+      <c r="K13" t="s">
+        <v>168</v>
+      </c>
+      <c r="L13" t="s">
+        <v>169</v>
+      </c>
+      <c r="M13" t="s">
+        <v>170</v>
+      </c>
+      <c r="N13" t="s">
+        <v>171</v>
+      </c>
+      <c r="O13" t="s">
+        <v>172</v>
+      </c>
+      <c r="P13" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>173</v>
+      </c>
+      <c r="R13" t="s">
+        <v>174</v>
       </c>
     </row>
-    <row r="8" spans="3:17">
-      <c r="C8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" t="s">
-        <v>96</v>
-      </c>
-      <c r="F8" t="s">
-        <v>97</v>
-      </c>
-      <c r="G8" t="s">
-        <v>98</v>
-      </c>
-      <c r="H8" t="s">
-        <v>99</v>
-      </c>
-      <c r="I8" t="s">
-        <v>100</v>
-      </c>
-      <c r="J8" t="s">
-        <v>101</v>
-      </c>
-      <c r="K8" t="s">
-        <v>102</v>
-      </c>
-      <c r="L8" t="s">
-        <v>103</v>
-      </c>
-      <c r="M8" t="s">
-        <v>104</v>
-      </c>
-      <c r="N8" t="s">
-        <v>105</v>
-      </c>
-      <c r="O8" t="s">
-        <v>106</v>
-      </c>
-      <c r="P8" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>108</v>
+    <row r="14" spans="3:18">
+      <c r="C14" t="s">
+        <v>175</v>
+      </c>
+      <c r="D14" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>176</v>
+      </c>
+      <c r="F14" t="s">
+        <v>177</v>
+      </c>
+      <c r="G14" t="s">
+        <v>178</v>
+      </c>
+      <c r="H14" t="s">
+        <v>179</v>
+      </c>
+      <c r="I14" t="s">
+        <v>180</v>
+      </c>
+      <c r="J14" t="s">
+        <v>181</v>
+      </c>
+      <c r="K14" t="s">
+        <v>182</v>
+      </c>
+      <c r="L14" t="s">
+        <v>183</v>
+      </c>
+      <c r="M14" t="s">
+        <v>184</v>
+      </c>
+      <c r="N14" t="s">
+        <v>185</v>
+      </c>
+      <c r="O14" t="s">
+        <v>186</v>
+      </c>
+      <c r="P14" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>188</v>
+      </c>
+      <c r="R14" t="s">
+        <v>189</v>
       </c>
     </row>
-    <row r="9" spans="3:17">
-      <c r="C9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" t="s">
-        <v>110</v>
-      </c>
-      <c r="E9" t="s">
-        <v>111</v>
-      </c>
-      <c r="F9" t="s">
-        <v>112</v>
-      </c>
-      <c r="G9" t="s">
-        <v>113</v>
-      </c>
-      <c r="H9" t="s">
-        <v>114</v>
-      </c>
-      <c r="I9" t="s">
-        <v>115</v>
-      </c>
-      <c r="J9" t="s">
-        <v>116</v>
-      </c>
-      <c r="K9" t="s">
-        <v>117</v>
-      </c>
-      <c r="L9" t="s">
-        <v>118</v>
-      </c>
-      <c r="M9" t="s">
-        <v>119</v>
-      </c>
-      <c r="N9" t="s">
-        <v>120</v>
-      </c>
-      <c r="O9" t="s">
-        <v>121</v>
-      </c>
-      <c r="P9" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="10" spans="3:17">
-      <c r="C10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" t="s">
-        <v>125</v>
-      </c>
-      <c r="G10" t="s">
-        <v>126</v>
-      </c>
-      <c r="H10" t="s">
-        <v>127</v>
-      </c>
-      <c r="I10" t="s">
-        <v>128</v>
-      </c>
-      <c r="J10" t="s">
-        <v>129</v>
-      </c>
-      <c r="K10" t="s">
-        <v>130</v>
-      </c>
-      <c r="L10" t="s">
-        <v>131</v>
-      </c>
-      <c r="M10" t="s">
-        <v>132</v>
-      </c>
-      <c r="N10" t="s">
-        <v>133</v>
-      </c>
-      <c r="O10" t="s">
-        <v>134</v>
-      </c>
-      <c r="P10" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="3:17">
-      <c r="C11" t="s">
-        <v>137</v>
-      </c>
-      <c r="D11" t="s">
-        <v>138</v>
-      </c>
-      <c r="E11" t="s">
-        <v>139</v>
-      </c>
-      <c r="F11" t="s">
-        <v>140</v>
-      </c>
-      <c r="G11" t="s">
-        <v>141</v>
-      </c>
-      <c r="H11" t="s">
-        <v>142</v>
-      </c>
-      <c r="I11" t="s">
-        <v>143</v>
-      </c>
-      <c r="J11" t="s">
-        <v>144</v>
-      </c>
-      <c r="K11" t="s">
-        <v>145</v>
-      </c>
-      <c r="L11" t="s">
-        <v>146</v>
-      </c>
-      <c r="M11" t="s">
-        <v>147</v>
-      </c>
-      <c r="N11" t="s">
-        <v>148</v>
-      </c>
-      <c r="O11" t="s">
-        <v>149</v>
-      </c>
-      <c r="P11" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="12" spans="3:17">
-      <c r="C12" t="s">
-        <v>151</v>
-      </c>
-      <c r="D12" t="s">
-        <v>152</v>
-      </c>
-      <c r="E12" t="s">
-        <v>153</v>
-      </c>
-      <c r="F12" t="s">
-        <v>154</v>
-      </c>
-      <c r="G12" t="s">
-        <v>155</v>
-      </c>
-      <c r="H12" t="s">
-        <v>156</v>
-      </c>
-      <c r="I12" t="s">
-        <v>157</v>
-      </c>
-      <c r="J12" t="s">
-        <v>154</v>
-      </c>
-      <c r="K12" t="s">
-        <v>154</v>
-      </c>
-      <c r="L12" t="s">
-        <v>154</v>
-      </c>
-      <c r="M12" t="s">
-        <v>158</v>
-      </c>
-      <c r="N12" t="s">
-        <v>154</v>
-      </c>
-      <c r="O12" t="s">
-        <v>154</v>
-      </c>
-      <c r="P12" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="13" spans="3:17">
-      <c r="C13" t="s">
-        <v>159</v>
-      </c>
-      <c r="D13" t="s">
-        <v>160</v>
-      </c>
-      <c r="E13" t="s">
-        <v>160</v>
-      </c>
-      <c r="F13" t="s">
-        <v>161</v>
-      </c>
-      <c r="G13" t="s">
-        <v>162</v>
-      </c>
-      <c r="H13" t="s">
-        <v>163</v>
-      </c>
-      <c r="I13" t="s">
-        <v>164</v>
-      </c>
-      <c r="J13" t="s">
-        <v>165</v>
-      </c>
-      <c r="K13" t="s">
-        <v>166</v>
-      </c>
-      <c r="L13" t="s">
-        <v>167</v>
-      </c>
-      <c r="M13" t="s">
-        <v>168</v>
-      </c>
-      <c r="N13" t="s">
-        <v>169</v>
-      </c>
-      <c r="O13" t="s">
-        <v>170</v>
-      </c>
-      <c r="P13" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="14" spans="3:17">
-      <c r="C14" t="s">
-        <v>172</v>
-      </c>
-      <c r="D14" t="s">
-        <v>173</v>
-      </c>
-      <c r="E14" t="s">
-        <v>174</v>
-      </c>
-      <c r="F14" t="s">
-        <v>175</v>
-      </c>
-      <c r="G14" t="s">
-        <v>176</v>
-      </c>
-      <c r="H14" t="s">
-        <v>177</v>
-      </c>
-      <c r="I14" t="s">
-        <v>178</v>
-      </c>
-      <c r="J14" t="s">
-        <v>179</v>
-      </c>
-      <c r="K14" t="s">
-        <v>180</v>
-      </c>
-      <c r="L14" t="s">
-        <v>181</v>
-      </c>
-      <c r="M14" t="s">
-        <v>182</v>
-      </c>
-      <c r="N14" t="s">
-        <v>183</v>
-      </c>
-      <c r="O14" t="s">
-        <v>184</v>
-      </c>
-      <c r="P14" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="15" spans="3:17">
+    <row r="15" spans="3:18">
       <c r="C15" t="s">
-        <v>187</v>
-      </c>
-      <c r="D15" t="s">
-        <v>188</v>
+        <v>190</v>
+      </c>
+      <c r="D15" s="4" t="b">
+        <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F15" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G15" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H15" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I15" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="J15" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K15" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L15" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M15" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N15" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O15" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P15" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q15" t="s">
-        <v>201</v>
+        <v>203</v>
+      </c>
+      <c r="R15" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excels/Local/L-Localization-通用.xlsx
+++ b/Config/Excels/Local/L-Localization-通用.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213">
   <si>
     <t>##var</t>
   </si>
@@ -134,6 +134,24 @@
   </si>
   <si>
     <t>越南语</t>
+  </si>
+  <si>
+    <t>common_user_name</t>
+  </si>
+  <si>
+    <t>账户名</t>
+  </si>
+  <si>
+    <t>UserName</t>
+  </si>
+  <si>
+    <t>common_user_password</t>
+  </si>
+  <si>
+    <t>密码</t>
+  </si>
+  <si>
+    <t>Password</t>
   </si>
   <si>
     <t>common_start_game</t>
@@ -663,9 +681,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -685,9 +709,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -695,13 +719,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -722,9 +739,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -732,7 +757,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -740,6 +765,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -755,17 +788,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -778,23 +811,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -815,85 +833,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -905,91 +1007,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1014,6 +1032,21 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1047,23 +1080,41 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1082,39 +1133,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1123,10 +1141,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="5">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
@@ -1135,133 +1153,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1601,7 +1619,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="16.125" style="2" customWidth="1"/>
@@ -1795,7 +1813,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="3:19">
+    <row r="4" customFormat="1" spans="2:7">
+      <c r="B4" s="2"/>
       <c r="C4" t="s">
         <v>40</v>
       </c>
@@ -1805,630 +1824,661 @@
       <c r="E4" t="s">
         <v>41</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4"/>
+      <c r="G4" t="s">
         <v>42</v>
       </c>
-      <c r="G4" t="s">
+    </row>
+    <row r="5" customFormat="1" spans="2:7">
+      <c r="B5" s="2"/>
+      <c r="C5" t="s">
         <v>43</v>
-      </c>
-      <c r="H4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J4" t="s">
-        <v>46</v>
-      </c>
-      <c r="K4" t="s">
-        <v>47</v>
-      </c>
-      <c r="L4" t="s">
-        <v>48</v>
-      </c>
-      <c r="M4" t="s">
-        <v>49</v>
-      </c>
-      <c r="N4" t="s">
-        <v>50</v>
-      </c>
-      <c r="O4" t="s">
-        <v>51</v>
-      </c>
-      <c r="P4" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>52</v>
-      </c>
-      <c r="R4" t="s">
-        <v>53</v>
-      </c>
-      <c r="S4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="3:19">
-      <c r="C5" t="s">
-        <v>55</v>
       </c>
       <c r="D5" s="5" t="b">
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F5" t="s">
-        <v>57</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="F5"/>
       <c r="G5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H5" t="s">
-        <v>59</v>
-      </c>
-      <c r="I5" t="s">
-        <v>60</v>
-      </c>
-      <c r="J5" t="s">
-        <v>61</v>
-      </c>
-      <c r="K5" t="s">
-        <v>62</v>
-      </c>
-      <c r="L5" t="s">
-        <v>63</v>
-      </c>
-      <c r="M5" t="s">
-        <v>64</v>
-      </c>
-      <c r="N5" t="s">
-        <v>65</v>
-      </c>
-      <c r="O5" t="s">
-        <v>66</v>
-      </c>
-      <c r="P5" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>67</v>
-      </c>
-      <c r="R5" t="s">
-        <v>68</v>
-      </c>
-      <c r="S5" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="3:19">
       <c r="C6" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D6" s="5" t="b">
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="F6" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="G6" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="H6" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="I6" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="J6" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="K6" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="L6" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="M6" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="N6" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="O6" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="P6" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="Q6" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="R6" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="S6" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="3:19">
       <c r="C7" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="D7" s="5" t="b">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="G7" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="H7" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="I7" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="J7" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="K7" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="L7" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="M7" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="N7" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="O7" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="P7" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="Q7" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="R7" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="S7" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="3:19">
       <c r="C8" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="D8" s="5" t="b">
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="F8" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="G8" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="I8" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="J8" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="K8" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="L8" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="M8" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="N8" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="O8" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="Q8" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="R8" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="S8" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="3:19">
       <c r="C9" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="D9" s="5" t="b">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="F9" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="G9" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="H9" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="I9" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="J9" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="K9" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="L9" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="M9" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="N9" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="P9" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="Q9" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="R9" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="S9" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="3:19">
       <c r="C10" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="D10" s="5" t="b">
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="G10" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="H10" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="I10" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="J10" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="K10" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="L10" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="M10" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="N10" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="O10" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="P10" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="Q10" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="R10" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="S10" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="3:19">
       <c r="C11" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="D11" s="5" t="b">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="F11" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="G11" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="H11" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="I11" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="J11" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="K11" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="L11" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="M11" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="N11" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="O11" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="P11" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="Q11" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="R11" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="S11" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="3:19">
       <c r="C12" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D12" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="G12" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="H12" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="I12" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="J12" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="K12" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="L12" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="M12" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="N12" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="O12" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="P12" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="Q12" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="R12" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="S12" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="3:19">
       <c r="C13" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="D13" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="F13" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="G13" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="H13" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="I13" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="J13" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="K13" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="L13" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="M13" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="N13" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="O13" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="P13" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="Q13" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="R13" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="S13" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" spans="3:19">
       <c r="C14" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="D14" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F14" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G14" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H14" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="I14" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="J14" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="K14" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="L14" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="N14" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="O14" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="P14" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="Q14" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="R14" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="S14" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="3:19">
       <c r="C15" t="s">
+        <v>170</v>
+      </c>
+      <c r="D15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>171</v>
+      </c>
+      <c r="F15" t="s">
+        <v>171</v>
+      </c>
+      <c r="G15" t="s">
+        <v>172</v>
+      </c>
+      <c r="H15" t="s">
+        <v>173</v>
+      </c>
+      <c r="I15" t="s">
+        <v>174</v>
+      </c>
+      <c r="J15" t="s">
+        <v>175</v>
+      </c>
+      <c r="K15" t="s">
+        <v>176</v>
+      </c>
+      <c r="L15" t="s">
+        <v>177</v>
+      </c>
+      <c r="M15" t="s">
+        <v>178</v>
+      </c>
+      <c r="N15" t="s">
+        <v>179</v>
+      </c>
+      <c r="O15" t="s">
+        <v>180</v>
+      </c>
+      <c r="P15" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>181</v>
+      </c>
+      <c r="R15" t="s">
+        <v>181</v>
+      </c>
+      <c r="S15" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="16" spans="3:19">
+      <c r="C16" t="s">
+        <v>183</v>
+      </c>
+      <c r="D16" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>184</v>
+      </c>
+      <c r="F16" t="s">
+        <v>185</v>
+      </c>
+      <c r="G16" t="s">
+        <v>186</v>
+      </c>
+      <c r="H16" t="s">
+        <v>187</v>
+      </c>
+      <c r="I16" t="s">
+        <v>188</v>
+      </c>
+      <c r="J16" t="s">
+        <v>189</v>
+      </c>
+      <c r="K16" t="s">
+        <v>190</v>
+      </c>
+      <c r="L16" t="s">
+        <v>191</v>
+      </c>
+      <c r="M16" t="s">
         <v>192</v>
       </c>
-      <c r="D15" s="5" t="b">
+      <c r="N16" t="s">
+        <v>193</v>
+      </c>
+      <c r="O16" t="s">
+        <v>194</v>
+      </c>
+      <c r="P16" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>195</v>
+      </c>
+      <c r="R16" t="s">
+        <v>196</v>
+      </c>
+      <c r="S16" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="17" spans="3:19">
+      <c r="C17" t="s">
+        <v>198</v>
+      </c>
+      <c r="D17" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="E15" t="s">
-        <v>193</v>
-      </c>
-      <c r="F15" t="s">
-        <v>194</v>
-      </c>
-      <c r="G15" t="s">
-        <v>195</v>
-      </c>
-      <c r="H15" t="s">
-        <v>196</v>
-      </c>
-      <c r="I15" t="s">
-        <v>197</v>
-      </c>
-      <c r="J15" t="s">
-        <v>198</v>
-      </c>
-      <c r="K15" t="s">
+      <c r="E17" t="s">
         <v>199</v>
       </c>
-      <c r="L15" t="s">
+      <c r="F17" t="s">
         <v>200</v>
       </c>
-      <c r="M15" t="s">
+      <c r="G17" t="s">
         <v>201</v>
       </c>
-      <c r="N15" t="s">
+      <c r="H17" t="s">
         <v>202</v>
       </c>
-      <c r="O15" t="s">
+      <c r="I17" t="s">
         <v>203</v>
       </c>
-      <c r="P15" t="s">
+      <c r="J17" t="s">
         <v>204</v>
       </c>
-      <c r="Q15" t="s">
-        <v>204</v>
-      </c>
-      <c r="R15" t="s">
+      <c r="K17" t="s">
         <v>205</v>
       </c>
-      <c r="S15" t="s">
+      <c r="L17" t="s">
         <v>206</v>
+      </c>
+      <c r="M17" t="s">
+        <v>207</v>
+      </c>
+      <c r="N17" t="s">
+        <v>208</v>
+      </c>
+      <c r="O17" t="s">
+        <v>209</v>
+      </c>
+      <c r="P17" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>210</v>
+      </c>
+      <c r="R17" t="s">
+        <v>211</v>
+      </c>
+      <c r="S17" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>
